--- a/offers/seasonal/عروض حليب بريمالاك وكيوت بيبي.xlsx
+++ b/offers/seasonal/عروض حليب بريمالاك وكيوت بيبي.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7DBEF9-0233-4D6F-ACB7-02E29AE01B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAF2649-013F-4830-BD0A-3E8CA9B331A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -49,31 +49,16 @@
     <t>1+1</t>
   </si>
   <si>
-    <t>00015095</t>
-  </si>
-  <si>
     <t>[00015095] بريمالاك بريماشور +1 400 جرام</t>
-  </si>
-  <si>
-    <t>00026659</t>
   </si>
   <si>
     <t>[00026659] بريمالاك بريماشور +3 400جم</t>
   </si>
   <si>
-    <t>00042496</t>
-  </si>
-  <si>
     <t>كيوت بيبي حليب الماعز رقم (1) 400 جرام</t>
   </si>
   <si>
-    <t>00042498</t>
-  </si>
-  <si>
     <t>كيوت بيبي حليب الماعز رقم (3) 400 جرام</t>
-  </si>
-  <si>
-    <t>00042497</t>
   </si>
   <si>
     <t>كيوت بيبي حليب الماعز رقم (2) 400 جرام</t>
@@ -144,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -163,6 +148,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,11 +524,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8">
+        <v>15095</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="3">
         <v>49.8</v>
@@ -561,11 +547,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
+      <c r="A3" s="8">
+        <v>26659</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
         <v>49.8</v>
@@ -584,17 +570,17 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
+      <c r="A4" s="8">
+        <v>42496</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3">
         <v>103.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4">
         <v>46295</v>
@@ -607,17 +593,17 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
+      <c r="A5" s="8">
+        <v>42498</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3">
         <v>103.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4">
         <v>46295</v>
@@ -630,17 +616,17 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" s="8">
+        <v>42497</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3">
         <v>103.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4">
         <v>46295</v>
